--- a/Uncertainty Budget.xlsx
+++ b/Uncertainty Budget.xlsx
@@ -468,7 +468,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="3">
-        <f t="shared" ref="G7:G11" si="0">B7*D7/F7</f>
+        <f>B7*D7/F7</f>
         <v>7.4999999999999997E-3</v>
       </c>
       <c r="H7" s="2" t="s">
@@ -496,7 +496,7 @@
         <v>1.7320508075688772</v>
       </c>
       <c r="G8" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G7:G11" si="0">B8*D8/F8</f>
         <v>2.0207259421636905E-3</v>
       </c>
     </row>
